--- a/tests/vlaanderen/reference/resultaten/werk/alle groepen/herkomsten/restdag/Pot_totaalproduct_Auto_OV.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/alle groepen/herkomsten/restdag/Pot_totaalproduct_Auto_OV.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>14052.97134230868</v>
+        <v>15161.00694743649</v>
       </c>
       <c r="C2">
-        <v>33102.37229944886</v>
+        <v>34484.58580207327</v>
       </c>
       <c r="D2">
-        <v>68743.10073124006</v>
+        <v>69790.0219535045</v>
       </c>
       <c r="E2">
-        <v>105891.1063534189</v>
+        <v>106843.4439530337</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>144215.7293901596</v>
+        <v>157206.6422077543</v>
       </c>
       <c r="C3">
-        <v>296666.0540025069</v>
+        <v>311371.9041552301</v>
       </c>
       <c r="D3">
-        <v>384373.8278992076</v>
+        <v>392128.5392423122</v>
       </c>
       <c r="E3">
-        <v>434779.1362784278</v>
+        <v>440449.3904941858</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>16114.21758240333</v>
+        <v>17651.97134614837</v>
       </c>
       <c r="C4">
-        <v>33507.08831302357</v>
+        <v>35217.50281128745</v>
       </c>
       <c r="D4">
-        <v>56697.23118320745</v>
+        <v>57884.57357059387</v>
       </c>
       <c r="E4">
-        <v>74514.34777728259</v>
+        <v>75544.07779570695</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>59789.47743706996</v>
+        <v>86794.69846744597</v>
       </c>
       <c r="C6">
-        <v>98642.60227902868</v>
+        <v>121432.266021457</v>
       </c>
       <c r="D6">
-        <v>105613.4204940141</v>
+        <v>116969.6732974113</v>
       </c>
       <c r="E6">
-        <v>94141.70156615564</v>
+        <v>97221.35885435728</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>6670.314300962499</v>
+        <v>8015.692504450645</v>
       </c>
       <c r="C7">
-        <v>16646.60103553965</v>
+        <v>18502.66186918269</v>
       </c>
       <c r="D7">
-        <v>20909.97910987132</v>
+        <v>22419.70389687472</v>
       </c>
       <c r="E7">
-        <v>24673.65696754771</v>
+        <v>25254.15625745019</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>489288.1990318958</v>
+        <v>606549.9971070047</v>
       </c>
       <c r="C9">
-        <v>981100.5988026557</v>
+        <v>1102624.270959345</v>
       </c>
       <c r="D9">
-        <v>1520489.714742828</v>
+        <v>1622053.417811703</v>
       </c>
       <c r="E9">
-        <v>2029455.228680691</v>
+        <v>2075955.457166761</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>543984.2287045494</v>
+        <v>591045.7349858725</v>
       </c>
       <c r="C12">
-        <v>834453.8850243824</v>
+        <v>871544.2418513163</v>
       </c>
       <c r="D12">
-        <v>848999.7934646605</v>
+        <v>863468.798641399</v>
       </c>
       <c r="E12">
-        <v>680032.5570383753</v>
+        <v>683217.4701666239</v>
       </c>
     </row>
     <row r="13" spans="1:5">
